--- a/Pivot Table.xlsx
+++ b/Pivot Table.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D89A67E2-EAEE-4301-83ED-20AE54C37E12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4AD4E7-ADB7-47C8-8AE1-980660500144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{2DFC34C7-759C-4DEF-BBE5-C49BAA4E6704}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{2DFC34C7-759C-4DEF-BBE5-C49BAA4E6704}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="5" r:id="rId3"/>
+  </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,10 +37,242 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
+  <si>
+    <t>Employee Name</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>City</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Department</t>
+  </si>
+  <si>
+    <t>Basic</t>
+  </si>
+  <si>
+    <t>JP Kumar</t>
+  </si>
+  <si>
+    <t>Andheri (W)</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>Training</t>
+  </si>
+  <si>
+    <t>Anjali Thakur</t>
+  </si>
+  <si>
+    <t>Govindpuri</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Accounts</t>
+  </si>
+  <si>
+    <t>Priya Agarwal</t>
+  </si>
+  <si>
+    <t>Sector 9</t>
+  </si>
+  <si>
+    <t>Marketing</t>
+  </si>
+  <si>
+    <t>R Vasu</t>
+  </si>
+  <si>
+    <t>Egmore</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>R&amp;D</t>
+  </si>
+  <si>
+    <t>Sanjay Gupta</t>
+  </si>
+  <si>
+    <t>Jharna Biswal</t>
+  </si>
+  <si>
+    <t>Link Road</t>
+  </si>
+  <si>
+    <t>Cuttack</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Prakash Dutta</t>
+  </si>
+  <si>
+    <t>Elgin Road</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>Manisha Guha</t>
+  </si>
+  <si>
+    <t>Alipore</t>
+  </si>
+  <si>
+    <t>Arjun Jain</t>
+  </si>
+  <si>
+    <t>MG Road</t>
+  </si>
+  <si>
+    <t>Arjun Kapoor</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>Abrar</t>
+  </si>
+  <si>
+    <t>Jayanagar</t>
+  </si>
+  <si>
+    <t>Shahid Khan</t>
+  </si>
+  <si>
+    <t>M.G Road</t>
+  </si>
+  <si>
+    <t>Mangalore</t>
+  </si>
+  <si>
+    <t>Anupam Mishra</t>
+  </si>
+  <si>
+    <t>Mysore</t>
+  </si>
+  <si>
+    <t>Ashwini</t>
+  </si>
+  <si>
+    <t>Prateek Babbar</t>
+  </si>
+  <si>
+    <t>North Road</t>
+  </si>
+  <si>
+    <t>Sukanya Reddy</t>
+  </si>
+  <si>
+    <t>Satish Puri</t>
+  </si>
+  <si>
+    <t>Bandra</t>
+  </si>
+  <si>
+    <t>Operation</t>
+  </si>
+  <si>
+    <t>Anjum Chopra</t>
+  </si>
+  <si>
+    <t>Worli</t>
+  </si>
+  <si>
+    <t>Akram Khan</t>
+  </si>
+  <si>
+    <t>S P B Road</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>Manish Grover</t>
+  </si>
+  <si>
+    <t>L L R Road</t>
+  </si>
+  <si>
+    <t>Noida</t>
+  </si>
+  <si>
+    <t>Emp Code</t>
+  </si>
+  <si>
+    <t>1.each dept total salary</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>sort the dept</t>
+  </si>
+  <si>
+    <t>then go to data tab</t>
+  </si>
+  <si>
+    <t>there select outlines</t>
+  </si>
+  <si>
+    <t>click subtotal</t>
+  </si>
+  <si>
+    <t>then select the required condition.</t>
+  </si>
+  <si>
+    <t>this will not create a separate table</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Sum of Basic</t>
+  </si>
+  <si>
+    <t>Average of Basic</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00;[Red]&quot;₹&quot;\ #,##0.00"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -64,8 +300,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -81,6 +327,398 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Varunesh.T" refreshedDate="46176.475309027781" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="20" xr:uid="{D4BC717F-ED19-4A13-9158-6DF74C81D890}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:G21" sheet="Sheet1"/>
+  </cacheSource>
+  <cacheFields count="7">
+    <cacheField name="Emp Code" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="20"/>
+    </cacheField>
+    <cacheField name="Employee Name" numFmtId="0">
+      <sharedItems/>
+    </cacheField>
+    <cacheField name="Address" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="City" numFmtId="0">
+      <sharedItems containsBlank="1"/>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="4">
+        <s v="W"/>
+        <s v="N"/>
+        <s v="S"/>
+        <s v="E"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Department" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Training"/>
+        <s v="Accounts"/>
+        <s v="Marketing"/>
+        <s v="R&amp;D"/>
+        <s v="Operation"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Basic" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="4500" maxValue="16250" count="9">
+        <n v="10000"/>
+        <n v="12000"/>
+        <n v="11250"/>
+        <n v="16250"/>
+        <n v="6400"/>
+        <n v="4500"/>
+        <n v="6275"/>
+        <n v="6250"/>
+        <n v="8750"/>
+      </sharedItems>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="20">
+  <r>
+    <n v="1"/>
+    <s v="JP Kumar"/>
+    <s v="Andheri (W)"/>
+    <s v="Mumbai"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="2"/>
+    <s v="Anjali Thakur"/>
+    <s v="Govindpuri"/>
+    <s v="Delhi"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="3"/>
+    <s v="Priya Agarwal"/>
+    <s v="Sector 9"/>
+    <m/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="4"/>
+    <s v="R Vasu"/>
+    <s v="Egmore"/>
+    <s v="Chennai"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="1"/>
+  </r>
+  <r>
+    <n v="5"/>
+    <s v="Sanjay Gupta"/>
+    <m/>
+    <s v="Delhi"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="6"/>
+    <s v="Jharna Biswal"/>
+    <s v="Link Road"/>
+    <s v="Cuttack"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="7"/>
+    <s v="Prakash Dutta"/>
+    <s v="Elgin Road"/>
+    <s v="Kolkata"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="8"/>
+    <s v="Manisha Guha"/>
+    <s v="Alipore"/>
+    <s v="Kolkata"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="9"/>
+    <s v="Arjun Jain"/>
+    <s v="MG Road"/>
+    <s v="Mumbai"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <n v="10"/>
+    <s v="Arjun Kapoor"/>
+    <m/>
+    <s v="Bangalore"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="11"/>
+    <s v="Abrar"/>
+    <s v="Jayanagar"/>
+    <s v="Bangalore"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="12"/>
+    <s v="Shahid Khan"/>
+    <s v="M.G Road"/>
+    <s v="Mangalore"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="0"/>
+  </r>
+  <r>
+    <n v="13"/>
+    <s v="Anupam Mishra"/>
+    <s v="Govindpuri"/>
+    <s v="Mysore"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="3"/>
+  </r>
+  <r>
+    <n v="14"/>
+    <s v="Ashwini"/>
+    <s v="Sector 9"/>
+    <s v="Mangalore"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="4"/>
+  </r>
+  <r>
+    <n v="15"/>
+    <s v="Prateek Babbar"/>
+    <s v="North Road"/>
+    <s v="Delhi"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="5"/>
+  </r>
+  <r>
+    <n v="16"/>
+    <s v="Sukanya Reddy"/>
+    <m/>
+    <s v="Mangalore"/>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="6"/>
+  </r>
+  <r>
+    <n v="17"/>
+    <s v="Satish Puri"/>
+    <s v="Bandra"/>
+    <s v="Mumbai"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="7"/>
+  </r>
+  <r>
+    <n v="18"/>
+    <s v="Anjum Chopra"/>
+    <s v="Worli"/>
+    <s v="Mumbai"/>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="8"/>
+  </r>
+  <r>
+    <n v="19"/>
+    <s v="Akram Khan"/>
+    <s v="S P B Road"/>
+    <s v="Pune"/>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="2"/>
+  </r>
+  <r>
+    <n v="20"/>
+    <s v="Manish Grover"/>
+    <s v="L L R Road"/>
+    <s v="Noida"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="0"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80596B12-67CB-426F-8C2B-582EA3A5FFC5}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0">
+      <items count="10">
+        <item x="5"/>
+        <item x="7"/>
+        <item x="6"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Average of Basic" fld="6" subtotal="average" baseField="4" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E347D732-3F3D-4CC0-8318-5410A71BCAE9}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="5"/>
+  </rowFields>
+  <rowItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Sum of Basic" fld="6" baseField="0" baseItem="0" numFmtId="164"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -379,10 +1017,664 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ACAA388-7626-4C9C-A583-5B10C4C7928F}">
+  <dimension ref="A3:B22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B3" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" s="3">
+        <v>33550</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="3">
+        <v>31500</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B6" s="3">
+        <v>17500</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B7" s="3">
+        <v>43300</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="3">
+        <v>58750</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="3">
+        <v>184600</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="3">
+        <v>5725</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="B19" s="3">
+        <v>10800</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="3">
+        <v>10132.142857142857</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="3">
+        <v>8500</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B22" s="3">
+        <v>9230</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F4D7EF4-42E1-439A-A87E-4144C4075885}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.08984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.26953125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G3" s="3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>14</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" s="3">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="3">
+        <v>12000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="3">
+        <v>16250</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
+        <v>28</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" t="s">
+        <v>31</v>
+      </c>
+      <c r="E8" t="s">
+        <v>28</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" t="s">
+        <v>31</v>
+      </c>
+      <c r="E9" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" s="3">
+        <v>6275</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>34</v>
+      </c>
+      <c r="C10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D10" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" t="s">
+        <v>9</v>
+      </c>
+      <c r="F10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" s="3">
+        <v>6250</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
+      </c>
+      <c r="F11" t="s">
+        <v>15</v>
+      </c>
+      <c r="G11" s="3">
+        <v>8750</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D12" t="s">
+        <v>37</v>
+      </c>
+      <c r="E12" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="3">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>40</v>
+      </c>
+      <c r="C13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D13" t="s">
+        <v>42</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
+        <v>23</v>
+      </c>
+      <c r="G13" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" t="s">
+        <v>44</v>
+      </c>
+      <c r="E14" t="s">
+        <v>22</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14" s="3">
+        <v>16250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" t="s">
+        <v>17</v>
+      </c>
+      <c r="D15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" t="s">
+        <v>22</v>
+      </c>
+      <c r="F15" t="s">
+        <v>15</v>
+      </c>
+      <c r="G15" s="3">
+        <v>6400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s">
+        <v>14</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="3">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>42</v>
+      </c>
+      <c r="E17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F17" t="s">
+        <v>23</v>
+      </c>
+      <c r="G17" s="3">
+        <v>6275</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" t="s">
+        <v>9</v>
+      </c>
+      <c r="F18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" s="3">
+        <v>6250</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>52</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" t="s">
+        <v>9</v>
+      </c>
+      <c r="F19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G19" s="3">
+        <v>8750</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E20" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" t="s">
+        <v>51</v>
+      </c>
+      <c r="G20" s="3">
+        <v>11250</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>57</v>
+      </c>
+      <c r="C21" t="s">
+        <v>58</v>
+      </c>
+      <c r="D21" t="s">
+        <v>59</v>
+      </c>
+      <c r="E21" t="s">
+        <v>14</v>
+      </c>
+      <c r="F21" t="s">
+        <v>10</v>
+      </c>
+      <c r="G21" s="3">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F27" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F28" t="s">
+        <v>63</v>
+      </c>
+      <c r="I28" s="4"/>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F29" t="s">
+        <v>64</v>
+      </c>
+      <c r="I29" s="4"/>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F30" t="s">
+        <v>65</v>
+      </c>
+      <c r="I30" s="4"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F31" t="s">
+        <v>66</v>
+      </c>
+      <c r="I31" s="4"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="F32" t="s">
+        <v>67</v>
+      </c>
+      <c r="I32" s="4"/>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:G21">
+    <sortCondition ref="A1:A21"/>
+  </sortState>
+  <mergeCells count="1">
+    <mergeCell ref="I27:I32"/>
+  </mergeCells>
+  <dataValidations count="3">
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B12:B16 B1:B5 B6:B9 B10:B11 B17:B21" xr:uid="{9B4F2714-5F7A-4E7C-BA7B-02FB485CE9A7}">
+      <formula1>ISTEXT(B1)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G1" xr:uid="{F2A3E1BF-FF82-4CE0-A6EA-327DBA2E4120}">
+      <formula1>ISNUMBER(G2)</formula1>
+    </dataValidation>
+    <dataValidation type="custom" operator="greaterThanOrEqual" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G12:G16 G2:G5 G6:G9 G10:G11 G17:G21" xr:uid="{7BB06D51-AD73-43B8-8F06-0CD93355015B}">
+      <formula1>ISNUMBER(G2)</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Pivot Table.xlsx
+++ b/Pivot Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Besant\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4AD4E7-ADB7-47C8-8AE1-980660500144}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC40B7F1-F009-47EC-881F-A7FDDEFE7933}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{2DFC34C7-759C-4DEF-BBE5-C49BAA4E6704}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{2DFC34C7-759C-4DEF-BBE5-C49BAA4E6704}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="75">
   <si>
     <t>Employee Name</t>
   </si>
@@ -254,6 +254,15 @@
   </si>
   <si>
     <t>Average of Basic</t>
+  </si>
+  <si>
+    <t>each department and each region wise number of employees</t>
+  </si>
+  <si>
+    <t>Count of Emp Code</t>
+  </si>
+  <si>
+    <t>Column Labels</t>
   </si>
 </sst>
 </file>
@@ -300,7 +309,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -312,11 +321,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="10">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="&quot;₹&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="&quot;₹&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="&quot;₹&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="&quot;₹&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="&quot;₹&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="&quot;₹&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="&quot;₹&quot;#,##0.00"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="171" formatCode="&quot;₹&quot;#,##0.00"/>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -572,6 +613,98 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FBE41220-4208-47C4-93B5-99A246BC0383}" name="PivotTable3" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="E15:K21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="7">
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="5">
+        <item x="3"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="6">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="4"/>
+        <item x="3"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="4"/>
+  </rowFields>
+  <rowItems count="5">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="5"/>
+  </colFields>
+  <colItems count="6">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="3"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of Emp Code" fld="0" subtotal="count" baseField="5" baseItem="0"/>
+  </dataFields>
+  <formats count="1">
+    <format dxfId="2">
+      <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
+    </format>
+  </formats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{80596B12-67CB-426F-8C2B-582EA3A5FFC5}" name="PivotTable2" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A17:B22" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
@@ -651,7 +784,7 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E347D732-3F3D-4CC0-8318-5410A71BCAE9}" name="PivotTable1" cacheId="5" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="7">
@@ -1018,14 +1151,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3ACAA388-7626-4C9C-A583-5B10C4C7928F}">
-  <dimension ref="A3:B22"/>
+  <dimension ref="A3:K22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.36328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.6328125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.26953125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.36328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.6328125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="5" t="s">
         <v>69</v>
       </c>
@@ -1033,7 +1173,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
@@ -1041,7 +1181,7 @@
         <v>33550</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>18</v>
       </c>
@@ -1049,7 +1189,7 @@
         <v>31500</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>51</v>
       </c>
@@ -1057,7 +1197,7 @@
         <v>17500</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>23</v>
       </c>
@@ -1065,7 +1205,7 @@
         <v>43300</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>10</v>
       </c>
@@ -1073,7 +1213,7 @@
         <v>58750</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>62</v>
       </c>
@@ -1081,47 +1221,174 @@
         <v>184600</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E13" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E15" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="E16" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="F16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G16" t="s">
+        <v>18</v>
+      </c>
+      <c r="H16" t="s">
+        <v>51</v>
+      </c>
+      <c r="I16" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" t="s">
+        <v>10</v>
+      </c>
+      <c r="K16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B17" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E17" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1</v>
+      </c>
+      <c r="G17" s="7">
+        <v>1</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7">
+        <v>1</v>
+      </c>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B18" s="3">
         <v>5725</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E18" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="F18" s="7">
+        <v>1</v>
+      </c>
+      <c r="G18" s="7">
+        <v>2</v>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7">
+        <v>2</v>
+      </c>
+      <c r="K18" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B19" s="3">
         <v>10800</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E19" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F19" s="7">
+        <v>2</v>
+      </c>
+      <c r="G19" s="7">
+        <v>1</v>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7">
+        <v>3</v>
+      </c>
+      <c r="J19" s="7">
+        <v>1</v>
+      </c>
+      <c r="K19" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>22</v>
       </c>
       <c r="B20" s="3">
         <v>10132.142857142857</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E20" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
+      <c r="H20" s="7">
+        <v>2</v>
+      </c>
+      <c r="I20" s="7">
+        <v>1</v>
+      </c>
+      <c r="J20" s="7">
+        <v>2</v>
+      </c>
+      <c r="K20" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>9</v>
       </c>
       <c r="B21" s="3">
         <v>8500</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E21" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F21" s="7">
+        <v>4</v>
+      </c>
+      <c r="G21" s="7">
+        <v>4</v>
+      </c>
+      <c r="H21" s="7">
+        <v>2</v>
+      </c>
+      <c r="I21" s="7">
+        <v>5</v>
+      </c>
+      <c r="J21" s="7">
+        <v>5</v>
+      </c>
+      <c r="K21" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>62</v>
       </c>
